--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487090_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487090_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.936</v>
+        <v>8.885</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0332</v>
+        <v>5.4105</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9028</v>
+        <v>3.4745</v>
       </c>
       <c r="G2" t="n">
         <v>6.2352</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3148</v>
+        <v>1.2638</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3022</v>
+        <v>0.6795</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0126</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4155</v>
+        <v>4.4066</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8638</v>
+        <v>2.2832</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5517</v>
+        <v>2.1234</v>
       </c>
       <c r="G3" t="n">
         <v>1.5216</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9941</v>
+        <v>0.9852</v>
       </c>
       <c r="T3" t="n">
-        <v>0.279</v>
+        <v>0.6984</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7151</v>
+        <v>0.2868</v>
       </c>
       <c r="V3" t="n">
         <v>1.5138</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6188</v>
+        <v>2.1607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7482</v>
+        <v>0.9553</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8706</v>
+        <v>1.2053</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4633</v>
+        <v>1.0063</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.862</v>
+        <v>-0.179</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3988</v>
+        <v>1.1853</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4097</v>
+        <v>0.6926</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2357</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6454</v>
+        <v>0.6512</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.873</v>
+        <v>0.3137</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3737</v>
+        <v>-0.2204</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2467</v>
+        <v>0.5341</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8468</v>
+        <v>0.3824</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3035</v>
+        <v>0.2628</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5433</v>
+        <v>0.1196</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6064</v>
+        <v>1.7037</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4546</v>
+        <v>0.0472</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1518</v>
+        <v>1.6565</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0063</v>
+        <v>-0.4633</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.179</v>
+        <v>-1.862</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1853</v>
+        <v>1.3988</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6926</v>
+        <v>0.4097</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>-2.2357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6512</v>
+        <v>2.6454</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3137</v>
+        <v>-0.873</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2204</v>
+        <v>0.3737</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5341</v>
+        <v>-1.2467</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1719</v>
+        <v>0.9317</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.238</v>
+        <v>0.6025</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.3291</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9559</v>
+        <v>1.14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9388</v>
+        <v>0.2771</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0171</v>
+        <v>0.8629</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2324</v>
+        <v>-0.6138</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4623</v>
+        <v>0.8528</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2299</v>
+        <v>-1.4666</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7521</v>
+        <v>0.3058</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1423</v>
+        <v>0.1187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6098</v>
+        <v>0.1871</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.9197</v>
       </c>
       <c r="N6" t="n">
-        <v>0.32</v>
+        <v>0.734</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8397</v>
+        <v>-1.6537</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.0881</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8252</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1554</v>
+        <v>1.1326</v>
       </c>
       <c r="T6" t="n">
-        <v>1.17</v>
+        <v>0.9363</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0146</v>
+        <v>0.1963</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6562</v>
+        <v>0.0422</v>
       </c>
       <c r="W6" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1857</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. LAMAZARES ABASCAL</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4333</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2141</v>
+        <v>0.8168</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2191</v>
+        <v>0.1242</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5727</v>
+        <v>2.2324</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1315</v>
+        <v>2.4623</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4413</v>
+        <v>-0.2299</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3926</v>
+        <v>2.7521</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3519</v>
+        <v>2.1423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0.6098</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1801</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2204</v>
+        <v>0.32</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4006</v>
+        <v>-0.8397</v>
       </c>
       <c r="P7" t="n">
-        <v>0.386</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5255</v>
+        <v>1.1405</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>1.048</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.347</v>
+        <v>0.0925</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>D. LAMAZARES ABASCAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3934</v>
+        <v>0.6732</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2018</v>
+        <v>0.3738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5952</v>
+        <v>0.2995</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6138</v>
+        <v>0.5727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8528</v>
+        <v>0.1315</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4666</v>
+        <v>0.4413</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3058</v>
+        <v>0.3926</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1187</v>
+        <v>0.3519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1871</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9197</v>
+        <v>0.1801</v>
       </c>
       <c r="N8" t="n">
-        <v>0.734</v>
+        <v>-0.2204</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6537</v>
+        <v>0.4006</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.386</v>
+        <v>-0.2855</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4574</v>
+        <v>-0.0188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.2667</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.309</v>
+        <v>0.0856</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3636</v>
+        <v>-1.2634</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0546</v>
+        <v>1.3491</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3704</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0615</v>
+        <v>0.4561</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2657</v>
+        <v>0.3659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2043</v>
+        <v>0.0902</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0988</v>
+        <v>-0.1509</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0947</v>
+        <v>-1.0933</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9959</v>
+        <v>0.9424</v>
       </c>
       <c r="G10" t="n">
         <v>0.1386</v>
@@ -1234,13 +1234,13 @@
         <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3067</v>
+        <v>1.2546</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2829</v>
+        <v>0.7185</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5896</v>
+        <v>0.536</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5796</v>
+        <v>-3.5806</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1967</v>
+        <v>-3.519</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3828</v>
+        <v>-0.0616</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7143</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8368</v>
+        <v>0.8358</v>
       </c>
       <c r="T11" t="n">
-        <v>1.17</v>
+        <v>0.8477</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3332</v>
+        <v>-0.0119</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.3719</v>
+        <v>16.2643</v>
       </c>
       <c r="E12" t="n">
-        <v>3.395900000000001</v>
+        <v>4.288199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>11.976</v>
+        <v>11.9762</v>
       </c>
       <c r="G12" t="n">
         <v>8.545</v>
       </c>
       <c r="H12" t="n">
-        <v>8.5129</v>
+        <v>8.512900000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03230000000000111</v>
+        <v>0.03230000000000066</v>
       </c>
       <c r="J12" t="n">
         <v>9.706500000000002</v>
@@ -1390,13 +1390,13 @@
         <v>13.5105</v>
       </c>
       <c r="S12" t="n">
-        <v>7.204700000000001</v>
+        <v>8.097200000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2484</v>
+        <v>6.1408</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9562</v>
+        <v>1.9561</v>
       </c>
       <c r="V12" t="n">
         <v>3.4824</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.221</v>
+        <v>2.246</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7171</v>
+        <v>0.7156</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5039</v>
+        <v>1.5304</v>
       </c>
       <c r="G13" t="n">
         <v>2.3761</v>
@@ -1468,13 +1468,13 @@
         <v>0.579</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3537</v>
+        <v>0.3787</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5415</v>
+        <v>0.54</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1877</v>
+        <v>-0.1613</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1228</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6272</v>
+        <v>0.1044</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0463</v>
+        <v>-0.6925</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4191</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6188</v>
+        <v>-1.1128</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3073</v>
+        <v>-1.302</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9261</v>
+        <v>0.1892</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6034</v>
+        <v>-0.3792</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5627</v>
+        <v>-0.4606</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0407</v>
+        <v>0.0814</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2222</v>
+        <v>-0.7336</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2554</v>
+        <v>-0.8414</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9668</v>
+        <v>0.1078</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.386</v>
+        <v>2.1231</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>1.632</v>
+        <v>-0.9059</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4079</v>
+        <v>-0.3133</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2241</v>
+        <v>-0.5926</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>J. SAEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3229</v>
+        <v>0.0615</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0931</v>
+        <v>0.8023</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7701</v>
+        <v>-0.7408</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1128</v>
+        <v>2.2104</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.302</v>
+        <v>0.9387</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1892</v>
+        <v>1.2717</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3792</v>
+        <v>2.0298</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4606</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>1.4245</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7336</v>
+        <v>0.1806</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8414</v>
+        <v>0.3335</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1078</v>
+        <v>-0.1528</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1231</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3332</v>
+        <v>-0.5123</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7139</v>
+        <v>-0.2624</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6194</v>
+        <v>-0.2499</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.6366</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6366</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.59</v>
+        <v>-0.4264</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7116</v>
+        <v>0.3393</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3016</v>
+        <v>-0.7657</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.985</v>
+        <v>-1.6691</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.5013</v>
+        <v>-3.3492</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5162</v>
+        <v>1.6801</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.5762</v>
+        <v>0.4797</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.8051</v>
+        <v>-1.506</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2288</v>
+        <v>1.9857</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4088</v>
+        <v>-2.1488</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6962</v>
+        <v>-1.8431</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7126</v>
+        <v>-0.3056</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5091</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6279</v>
+        <v>-0.7803</v>
       </c>
       <c r="T16" t="n">
-        <v>0.16</v>
+        <v>-0.4263</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7879</v>
+        <v>-0.354</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1278</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SAEZ PEREZ</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5108</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2015</v>
+        <v>-1.7998</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8744</v>
+        <v>1.289</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2104</v>
+        <v>0.3132</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9387</v>
+        <v>2.2346</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2717</v>
+        <v>-1.9214</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0298</v>
+        <v>-0.0278</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.0078</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4245</v>
+        <v>-2.0356</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1806</v>
+        <v>0.341</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3335</v>
+        <v>0.2268</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1528</v>
+        <v>0.1142</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2466</v>
+        <v>-1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8632</v>
+        <v>-0.1507</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3834</v>
+        <v>-0.8593</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6366</v>
+        <v>-0.779</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6366</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7105</v>
+        <v>-0.6832</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5318</v>
+        <v>0.5113</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8213</v>
+        <v>-1.1945</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7662</v>
+        <v>-3.985</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8425</v>
+        <v>-4.5013</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6087</v>
+        <v>0.5162</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2938</v>
+        <v>-1.5762</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>-2.8051</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3352</v>
+        <v>1.2288</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5276999999999999</v>
+        <v>-2.4088</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8011</v>
+        <v>-1.6962</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2735</v>
+        <v>-0.7126</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>2.5091</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2076</v>
+        <v>-0.7211</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.238</v>
+        <v>-0.0403</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0304</v>
+        <v>-0.6808</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1228</v>
+        <v>1.5138</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7514</v>
+        <v>-0.7083</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7998</v>
+        <v>0.8446</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0484</v>
+        <v>-1.5529</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3132</v>
+        <v>-0.6188</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2346</v>
+        <v>0.3073</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9214</v>
+        <v>-0.9261</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0278</v>
+        <v>1.6034</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0078</v>
+        <v>1.5627</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0356</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>0.341</v>
+        <v>-2.2222</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2268</v>
+        <v>-1.2554</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1142</v>
+        <v>-0.9668</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2506</v>
+        <v>0.2965</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1507</v>
+        <v>0.2062</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0999</v>
+        <v>0.0902</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.779</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2411</v>
+        <v>-0.7105</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2616</v>
+        <v>-1.5318</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9795</v>
+        <v>0.8213</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6691</v>
+        <v>-0.7662</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.3492</v>
+        <v>0.8425</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6801</v>
+        <v>-1.6087</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4797</v>
+        <v>-1.2938</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.506</v>
+        <v>0.0414</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9857</v>
+        <v>-1.3352</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1488</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8431</v>
+        <v>0.8011</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3056</v>
+        <v>-0.2735</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.595</v>
+        <v>-0.2076</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0271</v>
+        <v>-0.238</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5678</v>
+        <v>0.0304</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2859</v>
+        <v>-0.1228</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2809</v>
+        <v>-1.6199</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7667</v>
+        <v>-3.266</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4859</v>
+        <v>1.6461</v>
       </c>
       <c r="G21" t="n">
         <v>1.0358</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8078</v>
+        <v>-1.1468</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9518</v>
+        <v>-0.4511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.856</v>
+        <v>-0.6957</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7368</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7573</v>
+        <v>-3.1158</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3518</v>
+        <v>-1.9513</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4055</v>
+        <v>-1.1646</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1896</v>
@@ -2170,13 +2170,13 @@
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3398</v>
+        <v>-0.6983</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7442</v>
+        <v>-0.3437</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5956</v>
+        <v>-0.3546</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4439</v>
+        <v>-4.4563</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.241</v>
+        <v>-1.5067</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2029</v>
+        <v>-2.9496</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4731</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3835</v>
+        <v>-3.0885</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9104</v>
+        <v>2.4227</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5186</v>
+        <v>2.231</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6407</v>
+        <v>-0.3573</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1221</v>
+        <v>2.5883</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9546</v>
+        <v>-2.8968</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7428</v>
+        <v>-2.7312</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7883</v>
+        <v>-0.1657</v>
       </c>
       <c r="P23" t="n">
-        <v>0.386</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3161</v>
+        <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4726</v>
+        <v>-0.3163</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1361</v>
+        <v>-0.1404</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3365</v>
+        <v>-0.1759</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8842</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X23" t="n">
         <v>-1.228</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4493</v>
+        <v>-4.8851</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6068</v>
+        <v>-4.4413</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8425</v>
+        <v>-0.4438</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-2.4731</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0885</v>
+        <v>-3.3835</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4227</v>
+        <v>0.9104</v>
       </c>
       <c r="J24" t="n">
-        <v>2.231</v>
+        <v>-1.5186</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3573</v>
+        <v>-1.6407</v>
       </c>
       <c r="L24" t="n">
-        <v>2.5883</v>
+        <v>0.1221</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8968</v>
+        <v>-0.9546</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.7312</v>
+        <v>-1.7428</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1657</v>
+        <v>0.7883</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4741</v>
+        <v>0.386</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3511</v>
+        <v>2.3161</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3093</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2406</v>
+        <v>-0.3364</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0688</v>
+        <v>-0.5774</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.8842</v>
       </c>
       <c r="W24" t="n">
-        <v>1.228</v>
+        <v>-0.6562</v>
       </c>
       <c r="X24" t="n">
         <v>-1.228</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.372</v>
+        <v>-14.7044</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.9761</v>
+        <v>-11.9763</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3959</v>
+        <v>-2.7282</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.544899999999998</v>
+        <v>-8.5449</v>
       </c>
       <c r="H25" t="n">
         <v>-8.5129</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0320999999999998</v>
+        <v>-0.03210000000000079</v>
       </c>
       <c r="J25" t="n">
-        <v>1.161499999999999</v>
+        <v>1.1615</v>
       </c>
       <c r="K25" t="n">
         <v>-1.0985</v>
@@ -2389,7 +2389,7 @@
         <v>-9.706399999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.414199999999999</v>
+        <v>-7.4142</v>
       </c>
       <c r="O25" t="n">
         <v>-2.2922</v>
@@ -2404,13 +2404,13 @@
         <v>17.3707</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.204700000000002</v>
+        <v>-6.5372</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9562</v>
+        <v>-1.9564</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.248500000000001</v>
+        <v>-4.5809</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4825</v>
